--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_fea_001/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_fea_001/extracted.xlsx
@@ -485,6 +485,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -595,6 +600,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -630,6 +640,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G4" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -701,11 +716,6 @@
       </text>
     </comment>
     <comment ref="F6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1393,12 +1403,12 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Rank-ordering cementless femoral stem design variants and refining test plans under ISO 7206-4-like static loading</t>
+          <t>FEA-based design down-selection and test planning for a cementless Ti-6Al-4V femoral stem under ISO 7206-4-like static loads</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>A finite-element model of a press-fit Ti-6Al-4V hip stem in a composite femur is used to rank three design variants by peak stem stress, proximal cortical strain, and interface micromotion, and to guide instrumentation for subsequent bench testing. The model is not intended for per-patient prognosis, fatigue life prediction, or extreme activity analysis.</t>
+          <t>A finite-element model of a press-fit cementless hip stem seated in a composite femur is used to rank-order three design variants, estimate safety margins, and guide strain-gauge instrumentation placement prior to ISO 7206-4 bench testing. The model outputs peak von Mises stem stress, max principal cortical strain, and relative interface micromotion under two static load cases (2300 N axial and 3000 N + 20 Nm torsion). The model is not intended for per-patient prognosis, fatigue life prediction, or extreme-activity analysis.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1408,7 +1418,7 @@
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Class III</t>
+          <t>Class II</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
@@ -1432,9 +1442,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2030,7 +2040,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Design Down-Selection and Test Planning Requirement</t>
+          <t>Design Down-Selection Performance Requirement</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2040,7 +2050,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>The FEA model must reliably rank-order three stem design variants and identify instrumentation locations under ISO 7206-4-like static loads, with numerical errors small relative to design margins and comparisons to benchtop strain data demonstrating adequate agreement with quantified uncertainty.</t>
+          <t>The FEA model must correctly rank-order stem design variants and estimate safety margins (peak stem stress, cortical strain, and interface micromotion) under ISO 7206-4-like loading with numerical and comparison uncertainties small enough to resolve design differences of ~5–10% in the primary QoIs.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2062,13 +2072,13 @@
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>Hip Stem Structural FEA Model</t>
+          <t>Ansys Mechanical 2023 R2 FEA Model — Hip Stem</t>
         </is>
       </c>
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Ansys Mechanical 2023 R2 quasi-static structural FE model of a cementless Ti-6Al-4V stem press-fit into a Sawbones composite femur; augmented Lagrange frictional contact; 10-node tetrahedral elements; outputs von Mises stress, cortical principal strain, and interface micromotion.</t>
+          <t>Quasi-static structural FEA model of a Ti-6Al-4V size-6 cementless femoral stem press-fitted into a Sawbones fourth-generation composite femur; includes frictional contact, press-fit interference, and homogenized porous-coating layer; run in Ansys Mechanical 2023 R2 with sparse direct solver and augmented Lagrange contact.</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2082,13 +2092,13 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>Composite Femur Bench Strain Gauge Dataset</t>
+          <t>Composite Femur Strain-Gauge Benchtop Dataset</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Strain gauge measurements from five Sawbones 3403 composite femurs under two static load cases (2300 N and 3000 N + 20 Nm); six cortical gauges per specimen plus two stem-shoulder rosettes; used as the experimental comparator for validation.</t>
+          <t>Strain measurements from six 350-ohm gauges on five nominally identical Sawbones 3403 composite femurs instrumented under two static load cases (Case A: 2300 N; Case B: 3000 N + 20 Nm), with factory-certified gauge calibration and in-situ shunt verification; standard deviation across five repeats ≤ 30 με.</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2102,13 +2112,13 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>Porous Coating and Friction Coefficient Characterization Data</t>
+          <t>Porous Coating and Friction Coefficient Test Data</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Compression stiffness of coated coupons (n=6) used to calibrate the homogenized coating modulus (8.5 GPa), and push-out test data on coated plugs in composite shells (n=5) yielding friction coefficient 0.42 ± 0.06.</t>
+          <t>Independent coupon compression tests (n=6) for porous coating homogenized modulus (8.5 GPa) and push-out tests (n=5) for friction coefficient μ=0.42 ± 0.06; used as model inputs without tuning against femur-level validation data.</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -2258,7 +2268,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Cantilever Beam and Thick-Walled Cylinder Analytical Benchmarks</t>
+          <t>Cortical Strain Comparison — Case A (2300 N Axial)</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2273,27 +2283,27 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Element formulations verified by comparing FE predictions to analytical solutions for a cantilever beam under end load and a thick-walled cylinder under internal pressure.</t>
+          <t>FEA-predicted area-averaged cortical strains at five gauge locations compared to mean bench measurements from five composite femur specimens under ISO-like 2300 N axial load at 10° adduction, 9° flexion.</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Timoshenko beam theory tip deflection and fixed-end stress; Lamé thick-walled cylinder radial stress solution</t>
+          <t>Benchtop strain-gauge measurements on Sawbones 3403 composite femurs</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
-        <is>
-          <t>Quantitative result if applicable</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="39" t="inlineStr">
+        <is>
+          <t>Standard error propagation combining model uncertainty and gauge measurement error; 95% prediction interval</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>Cantilever tip deflection error 0.6%, fixed-end stress error 1.4%; cylinder L2 radial stress error &lt;0.8%</t>
+          <t>MAPD 6.8%; NRMSE 8.9%; 95% PI enveloped 83% of observed gauge means; all gauge signs matched</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -2305,7 +2315,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Hertzian Contact Benchmark</t>
+          <t>Cortical Strain Comparison — Case B (3000 N + 20 Nm)</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2316,23 +2326,27 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Augmented Lagrange contact enforcement verified against Hertzian line-contact analytical solution for peak contact pressure and patch width.</t>
+          <t>FEA-predicted cortical strains at five gauge locations compared to bench measurements under combined 3000 N axial and 20 Nm internal rotation moment load case.</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Hertzian analytical solution (Johnson, Contact Mechanics)</t>
+          <t>Benchtop strain-gauge measurements on Sawbones 3403 composite femurs</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G4" s="33" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" s="41" t="inlineStr">
+        <is>
+          <t>Standard error propagation; 95% prediction interval from surrogate-based UQ</t>
+        </is>
+      </c>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>Peak contact pressure within 3.2%; contact patch width within 2.5%</t>
+          <t>MAPD 9.7%; NRMSE 11.8%</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2344,7 +2358,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study (Richardson Extrapolation)</t>
+          <t>Mesh Convergence and Discretization Error Study</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2355,12 +2369,12 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Three systematically refined meshes assessed for peak stem von Mises stress, max principal cortical strain at Gruen 7, and interface micromotion; order of accuracy ~1.9–2.1; remaining discretization errors estimated by Richardson extrapolation.</t>
+          <t>Three systematically refined meshes (h, h/√2, h/2) assessed for peak stem stress, max principal cortical strain, and micromotion amplitude; Richardson extrapolation used to estimate remaining discretization error; observed convergence order ~1.9–2.1.</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Grid-extrapolated asymptotic values</t>
+          <t>Richardson extrapolation grid-independent estimates</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
@@ -2370,12 +2384,12 @@
       </c>
       <c r="G5" s="41" t="inlineStr">
         <is>
-          <t>Richardson extrapolation; additive variance propagated into QoI uncertainty bounds</t>
+          <t>Richardson extrapolation; discretization uncertainty propagated additively into overall UQ</t>
         </is>
       </c>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>Peak stem stress 2.1%; max cortical strain 3.4%; micromotion 5.6% of extrapolated value</t>
+          <t>Peak stem stress residual 2.1%; cortical strain residual 3.4%; micromotion residual 5.6%</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -2387,7 +2401,7 @@
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Cortical Strain Gauge Comparison — Case A and Case B</t>
+          <t>Solver Correctness Benchmarks (Patch Test and Analytical Solutions)</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2398,27 +2412,23 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>FE-predicted cortical strains compared to bench measurements at five gauge locations on five composite femurs under two load cases; virtual gauge areas area-averaged over 3.2 × 3.2 mm patches matching experimental gauge grids.</t>
+          <t>Element formulations verified via constant-strain patch test; tip deflection and fixed-end stress of cantilever beam; radial stress field in thick-walled cylinder (Lamé); peak contact pressure and patch width in Hertzian line contact problem.</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>Strain gauge measurements on five Sawbones 3403 composite femurs</t>
+          <t>Analytical solutions (Timoshenko beam, Lamé cylinder, Hertz contact)</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="41" t="inlineStr">
-        <is>
-          <t>Standard error propagation combining model uncertainty and measurement error; 95% prediction interval coverage assessed</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" s="33" t="n"/>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>Case A MAPD 6.8%, NRMSE 8.9%; Case B MAPD 9.7%, NRMSE 11.8%; 95% PI enveloped 83% of observed gauge means</t>
+          <t>Cantilever tip deflection error 0.6%; fixed-end stress error 1.4%; Lamé L2 error &lt;0.8%; Hertz peak pressure within 3.2%; patch width within 2.5%</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2430,7 +2440,7 @@
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>Global Sensitivity and Uncertainty Quantification via Kriging Surrogate</t>
+          <t>Global Sensitivity and Uncertainty Propagation</t>
         </is>
       </c>
       <c r="B7" s="41" t="inlineStr">
@@ -2441,12 +2451,12 @@
       <c r="C7" s="33" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>200 Latin hypercube samples across seven input parameters propagated through a kriging surrogate trained on 60 high-fidelity FE runs; Sobol indices computed; 95% uncertainty intervals produced for all three primary QoIs.</t>
+          <t>Latin hypercube sampling (200 samples) with kriging surrogate trained on 60 high-fidelity FE runs; Sobol first-order indices computed for seven input parameters; 95% uncertainty intervals propagated for all three QoIs.</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>High-fidelity FE runs (cross-validation RMSE &lt;3% for QoIs)</t>
+          <t>Kriging surrogate cross-validated RMSE &lt;3% for QoIs</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
@@ -2456,7 +2466,7 @@
       </c>
       <c r="G7" s="41" t="inlineStr">
         <is>
-          <t>Latin hypercube sampling, Sobol sensitivity indices, kriging surrogate with cross-validation</t>
+          <t>Sobol sensitivity indices via kriging surrogate; Latin hypercube sampling</t>
         </is>
       </c>
       <c r="H7" s="41" t="inlineStr">
@@ -2685,12 +2695,12 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercial solver with documented QA controls and reproducible results</t>
+          <t>Simulation software must be commercially maintained and verified to produce reliable results for the governing physics.</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>Ansys Mechanical 2023 R2 is a widely certified commercial solver. An internal benchmark suite of 12 elasticity problems was executed upon environment update and passed prior to study start (Appendix A1). All scripts and models are version-controlled in GitLab (tag v1.8) with archived checksums, solver options, and run manifests. Three independent reruns of the baseline case reproduced reaction forces and strains within 0.2%. Platform and solver settings are fully documented.</t>
+          <t>Ansys Mechanical 2023 R2 is a validated commercial solver. An internal benchmark suite of 12 elasticity problems was executed upon environment update prior to study start (Appendix A1). Three independent reruns of the baseline case produced identical results to within 0.2%, demonstrating deterministic reproducibility. All scripts and model files are version-controlled in GitLab (HSTEM-FEA, tag v1.8) with archived run manifests including software versions, solver options, and checksums. Platform is a controlled Windows Server 2019 environment.</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2718,12 +2728,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Code correctly solves governing equations for relevant element types and contact formulations</t>
+          <t>Element formulations and contact algorithms must be shown to correctly solve the governing equations for the relevant physics class.</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Patch test for TET10 and HEX8 elements recovers constant strain within machine tolerance. Cantilever beam tip deflection error 0.6% and fixed-end stress error 1.4% vs. analytical solution. Thick-walled cylinder radial stress L2 error &lt;0.8% vs. Lamé solution. Hertzian line contact peak pressure within 3.2% and patch width within 2.5% vs. Johnson analytical solution. All governing physics types (elasticity, contact) are covered by analytical benchmarks.</t>
+          <t>Four analytical/benchmark problems directly relevant to the model physics were executed: (1) constant-strain patch test for hex and tet elements passing to machine tolerance; (2) cantilever beam tip deflection within 0.6% and fixed-end stress within 1.4% of Timoshenko beam theory; (3) thick-walled cylinder Lamé radial stress field with L2 error &lt;0.8%; (4) Hertzian line contact peak pressure within 3.2% and patch width within 2.5% using the augmented Lagrange contact algorithm employed in the study. These benchmarks cover all primary element types and the contact enforcement method used.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2751,12 +2761,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with quantified remaining discretization error for all primary QoIs</t>
+          <t>Discretization error in primary QoIs must be characterized and shown to be small relative to design differences being resolved (~5–10%).</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three systematically refined meshes (h, h/√2, h/2) were used; all three primary QoIs showed monotonic convergence. Order of accuracy 1.9–2.1 is consistent with quadratic tet formulation. Richardson extrapolation yields residual discretization errors of 2.1% (peak stem stress), 3.4% (cortical strain), and 5.6% (micromotion). Mesh-induced variability is propagated additively into the overall QoI uncertainty bounds. Baseline (middle) mesh selected for parametric studies.</t>
+          <t>A formal three-level mesh refinement study (h, h/√2, h/2) was performed on all three QoIs. Monotonic convergence was observed with estimated order of accuracy ~1.9–2.1, consistent with quadratic tet elements. Richardson extrapolation yielded residual discretization errors of 2.1% (peak stem stress), 3.4% (cortical strain), and 5.6% (micromotion) for the baseline mesh. These values are explicitly propagated as additive variance into the overall uncertainty budget (Section 8.2). The micromotion discretization error (5.6%) is the largest but remains within the 14.3% combined 95% interval.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2784,12 +2794,12 @@
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Iterative solver convergence verified with documented residual targets and energy balance</t>
+          <t>Iterative solver convergence must be confirmed; residuals must meet targets; contact must not exhibit numerical instability.</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Force residual target 1e-4, displacement change target 1e-6 m, contact penetration target &lt;2 μm documented. Contact status monotonic after first two substeps with no chattering. Energy balance verified: external work minus internal strain energy equals reaction work within 0.5%. Reruns under stricter tolerances changed outputs less than 0.3%, confirming solver convergence is not a meaningful error source.</t>
+          <t>Force residual target 1e-4 and displacement change target 1e-6 m were applied. Contact penetration target was &lt;2 μm at closure with 25 maximum equilibrium iterations per substep and automatic substepping. Contact status was monotonic after the first two substeps with no chattering reported. Energy balance (external work minus internal strain energy vs. reaction work) was verified to within 0.5%. Reruns under stricter tolerances changed all outputs by less than 0.3%, confirming solver convergence is not a significant error source.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2817,12 +2827,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent review of model setup, boundary conditions, and post-processing; documented analysis plan</t>
+          <t>Model setup (boundary conditions, load application, geometry, material assignment) must be independently reviewed and verified against the analysis plan.</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>Model development followed written analysis plan ADP-ORTHO-022 rev B. A separate analyst independently reviewed mesh, contact definitions, and load mapping; 14 review comments all resolved and tracked in issue tracker. External biomechanics SME conducted a 2-hour review of validation methodology and comparator appropriateness with no critical deficiencies. Virtual gauge mapping procedure documented in Appendix A2. Load vectors and potting boundary verified against lab coordinate frames.</t>
+          <t>Model development followed a written analysis plan (ADP-ORTHO-022, rev B). A separate analyst performed an independent peer review of the mesh, contact definitions, and load mapping; 14 review comments were raised and all closed in the issue tracker. An external biomechanics SME conducted a 2-hour review of validation methodology and comparator appropriateness with no critical deficiencies identified. A virtual gauge-area mapping approach (Appendix A2) was used to verify FE-to-experiment location alignment. Boundary condition consistency was confirmed by checking that reaction moments match lab fixtures.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2850,12 +2860,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Governing equations and key modeling assumptions justified for the intended physics regime</t>
+          <t>The mathematical model form (governing equations, contact representation, material assumptions) must be justified for the COU physics regime.</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>Quasi-static, small-strain linear elastic formulation is justified by the load levels and by the absence of observed plasticity in bench tests. Contact nonlinearity and press-fit interference are explicitly included. Porous coating homogenization is supported by independent coupon compression tests. Limitations are explicitly documented: no fatigue, no bone remodeling, no time-dependent phenomena, no cadaveric anatomy. Transversely isotropic composite femur orthotropy is justified by vendor data and ultrasonic verification (Appendix A3).</t>
+          <t>Quasi-static structural mechanics with frictional contact and press-fit interference is justified for the load levels considered (no plasticity observed in bench tests; small-strain assumption validated by measurements). Geometric nonlinearity is limited to contact closure, which is appropriate. The porous coating homogenization is supported by coupon-level compression tests. Composite femur orthotropic layup is represented as transversely isotropic, consistent with published vendor data. Known limitations (no fatigue, no bone remodeling, no time-dependent phenomena) are explicitly documented. The model does not cover anatomical variability or extreme activities.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2883,12 +2893,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Key material properties and boundary conditions characterized from independent tests or standards, with uncertainty documented</t>
+          <t>Key material properties and boundary condition inputs must be traceable to measurements or standards, with uncertainty characterized for dominant inputs.</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>Ti-6Al-4V properties from ASTM F136 and internal QA coupons. Composite femur orthotropy from vendor datasheet verified by ultrasonic C-scan (Appendix A3). Porous coating modulus calibrated from n=6 coupon compression tests (8.5 GPa) without tuning against femur strains. Friction coefficient from n=5 dedicated push-out tests (μ=0.42 ± 0.06). Press-fit interference from reamer/stem gauge with ±10 μm tolerance. Load angle and seating depth tolerances reflect documented fixture capabilities. Input uncertainty ranges propagated through surrogate model.</t>
+          <t>Ti-6Al-4V properties (E=110 GPa, ν=0.34) are sourced from ASTM F136 and internal QA coupons. Composite femur orthotropic properties come from the vendor datasheet and were independently verified by ultrasonic C-scan (Appendix A3). Porous coating modulus (8.5 GPa) was derived from n=6 coupon compression tests without tuning against femur-level data. Friction coefficient (μ=0.42 ± 0.06) was measured via n=5 push-out tests on coated plugs. Press-fit interference (50 μm) is traceable to reamer and stem gauge dimensions with ±10 μm tolerance. Load angles and seating depth reflect fixture capabilities. Sobol sensitivity analysis identified the dominant inputs, and uncertainty ranges were formally propagated.</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2916,12 +2926,12 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Sufficient specimens with documented characteristics and production-representative construction</t>
+          <t>Experimental test articles must be sufficiently characterized and representative of the modeled structure.</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>Five nominally identical Sawbones 3403 composite femurs used; seating depth controlled to within 0.5 mm of FE geometry. Composite femur orthotropic layup is published and repeatable per vendor; modulus distribution verified by micro-CT on one specimen. Strain gauge repeatability standard deviation ≤30 με at peaks of 600–800 με across five repeats per load. Sample size (n=5) is modest but adequate for a composite analog comparator at this decision stage; human cadaver variability is explicitly noted as out of scope.</t>
+          <t>Five nominally identical Sawbones 3403 fourth-generation composite femurs were used. Seating depth was controlled within 0.5 mm of the FE geometry; one specimen was micro-CT verified for seating consistency. The composite femur orthotropic layup is known, repeatable, and published by the vendor. Sample size of n=5 enables basic repeatability assessment; strain repeatability SD ≤ 30 με at peak strains of 600–800 με. The composite bone analog is acknowledged as not being human bone; cadaver validation is planned for future phases. The sample population does not cover anatomical variability.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -2949,12 +2959,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Controlled and calibrated test environment with documented measurement uncertainty</t>
+          <t>Test conditions must be controlled and instrumented with calibrated equipment and documented measurement uncertainty.</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>Load applied through custom head/neck adaptor at 10° adduction and 9° flexion per ISO 7206-4 guidance. Crosshead load cell calibrated to 0.5% FS; ancillary torque cell to 1% FS. Six 350-ohm strain gauges factory certified; in-situ shunt calibration confirmed drift &lt;0.4% FS. Gauge placement tolerance ±1 mm, orientation ±2°. Temperature controlled at 21°C dry. Two static load cases per specimen with documented repeatability. Distal potting in epoxy with 70 mm embedment standardized across specimens.</t>
+          <t>Tests conducted at 21°C, dry; environment was controlled. Load application followed ISO 7206-4 line-of-action guidance (10° adduction, 9° flexion). Crosshead load cell calibrated to 0.5% FS; ancillary torque cell to 1% FS. Six 350-ohm strain gauges (3.2 mm grid) factory certified with in-situ shunt calibration verifying drift &lt;0.4% FS; placement tolerance ±1 mm, orientation ±2°. Two rosettes at stem shoulder used qualitatively. Strain measurement repeatability SD ≤ 30 με across five repeats per load. Distal potting controlled to 70 mm embedment in an aluminum cup with epoxy.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -2982,12 +2992,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>Model inputs demonstrably match experimental boundary conditions, with mapping of geometry, loads, and constraints</t>
+          <t>Model input parameters must demonstrably match experimental test conditions, with discrepancies identified and their effects quantified.</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Potting boundary and load vectors explicitly aligned to lab coordinate frames. Virtual gauge areas computed as area-averages over the 3.2 × 3.2 mm patch projected along gauge orientation (Appendix A2). Rigid link replicates neck adaptor stiffness (100 kN/mm); sensitivity confirmed negligible effect. Femoral anteversion fixed at 15° to match jig. Insertion axis and seating depth set to match jig geometry. Both load cases (A and B) replicated with matching resultant magnitudes, directions, and torque. Input uncertainty from experimental setup (load angle, seating depth) propagated into model outputs.</t>
+          <t>Load vectors (magnitude, direction, application point) were matched to lab coordinate frames; rigid link replicating neck adaptor stiffness (100 kN/mm) was included with sensitivity analysis confirming negligible effect. Potting boundary conditions replicated distal 70 mm embedment with fixed-DOF rigid socket. Gauge locations in FE were taken as area-averaged over the 3.2 × 3.2 mm patch projected along the gauge orientation, matching physical gauge size and alignment (Appendix A2). Seating depth and anteversion matched to fixture geometry. Measurement uncertainty from gauge calibration and placement tolerance was included in combined uncertainty propagation. Key model inputs (μ, coating modulus) have characterized uncertainties propagated through the comparison.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3015,12 +3025,12 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative agreement metrics reported for all primary QoIs with uncertainty bands; sign and trend agreement confirmed</t>
+          <t>Quantitative comparison of model predictions to experimental measurements must demonstrate acceptable agreement with uncertainty quantification.</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Case A cortical strain: MAPD 6.8%, NRMSE 8.9% across five gauge locations. Case B: MAPD 9.7%, NRMSE 11.8%. All gauge signs and directions matched. Combined 95% prediction interval enveloped 83% of observed gauge means. Stem shoulder rosette principal directions within 7°, magnitudes within 12% (qualitative due to geometry difference noted). Uncertainty propagation combines model and measurement sources. Two load cases reported. Metrics are clearly defined and consistently applied.</t>
+          <t>Case A: MAPD 6.8% and NRMSE 8.9% across five cortical gauge locations; all gauge signs matched. Case B: MAPD 9.7% and NRMSE 11.8%. Combined model and measurement 95% prediction interval enveloped 83% of observed gauge means across specimens. Stem shoulder rosette principal directions agreed within 7° and magnitudes within 12% (qualitative comparison only due to geometry difference). Uncertainty was computed via standard error propagation combining model UQ (Section 8.2) and measurement error. Two load cases provide comparison at two points in the load envelope. Comparison methodology, including virtual gauge mapping, is fully documented.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3048,12 +3058,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>Model outputs directly address the decision (design ranking and test planning) and are measurable both computationally and experimentally</t>
+          <t>The model QoIs must directly correspond to the design decision criteria and must be measurable both computationally and experimentally.</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>The three primary QoIs — peak von Mises stress at stem fillets, max principal cortical strain at Gruen zones 1 and 7, and interface micromotion — directly correspond to design screening criteria (static strength margin, periprosthetic strain environment, and osseointegration potential). All three are computed in the FE model and the first two are measured experimentally at the same locations using strain gauges. Micromotion is a computed-only QoI at this stage but is the dominant output for interface fixation assessment and is tied to validated boundary conditions. The QoIs are directly linked to test instrumentation planning decisions.</t>
+          <t>The three primary QoIs (peak von Mises stem stress at neck/shoulder fillets, max principal cortical strain near Gruen zones 1 and 7, and relative interface micromotion) directly map to the design down-selection criteria: structural integrity margin, peri-prosthetic bone loading, and osseointegration risk indicator. Cortical strain and stem stress are measurable experimentally via strain gauges (and rosettes) and in the FE model using matched area-averaging. Micromotion is computed in the FE model and is the target of interest for porous-coating fixation decisions. The outputs also directly guide gauge placement for the subsequent bench test program. QoIs are directly referenced in the decision outcome summary (Section 12).</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3081,12 +3091,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions (geometry, loads, physics regime) match the intended use; gaps documented</t>
+          <t>Validation conditions must match or adequately represent the intended operating conditions, geometry, and physics regime of the COU.</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Validation used the same stem geometry family, same composite femur, same loading fixture, and same two load cases (ISO 7206-4-like 2300 N and combined 3000 N + 20 Nm) as the COU. The validated load envelope spans 2.3–3.0 kN resultant and up to 20 Nm torsion, which covers the primary design evaluation window. Gaps explicitly documented: composite femur is not human bone (cadaver validation planned for next phase), only one size validated, and activities beyond 3.0 kN or 20 Nm are flagged as extrapolations. Extrapolation warnings embedded in post-processing scripts. Scope is appropriate for the stated preclinical decision-support use.</t>
+          <t>Validation was performed using the same stem geometry, composite femur analog, loading protocol (ISO 7206-4 line-of-action), and load magnitudes (2.3–3.0 kN, up to 20 Nm torsion) as the intended COU. The validated load envelope directly covers the design evaluation conditions. Extrapolation warnings are embedded in post-processing scripts for loads outside the validated window. Acknowledged gaps: (1) only the composite bone analog, not cadaveric human bone, was used; (2) only one stem size and neck option were validated; (3) activities above 3.0 kN or beyond 20 Nm torsion are explicitly flagged as outside the validated regime. A maturation roadmap for extended use cases is provided (Appendix A4). These gaps are appropriate given the stated COU but limit the factor to level 3.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3175,7 +3185,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>For the bounded context of use — rank-ordering cementless femoral stem design variants and guiding bench test instrumentation under ISO 7206-4-like static loads — the model meets the required rigor for MRL 3 at a Medium assurance level. Numerical errors are quantified and small relative to design margins (discretization errors 2.1–5.6%; solver convergence verified via energy balance and residual checks). Key inputs are tied to independent experimental data with documented uncertainty. Cortical strain predictions agree with five-specimen bench measurements within MAPD 6.8–9.7% across two load cases, with sign and trend agreement, and uncertainty propagation is complete. Independent peer review and external SME review were completed with no critical deficiencies. Limitations — composite analog (not human bone), single size, restricted load envelope — are explicitly documented and do not undermine the stated decision. The model is not accepted for per-patient risk assessment, fatigue life prediction, or loading beyond the validated envelope without additional evidence.</t>
+          <t>For the bounded COU of design variant down-selection and bench-test instrumentation planning under ISO 7206-4-like static loads, all 13 credibility factors meet or exceed their required levels. Numerical discretization errors are small relative to design differences (2.1–5.6%); solver correctness is demonstrated against analytical benchmarks; key inputs are traceable to independent tests with quantified uncertainty; global sensitivity analysis identifies dominant parameters; and quantitative comparison to benchtop strain measurements shows MAPD of 6.8–9.7% with matched signs and trends, with a 95% prediction interval enveloping 83% of observed data. Independent peer review and SME review are documented and closed. The model is accepted for the stated COU with the following conditions: (1) use is restricted to the validated load envelope (2.3–3.0 kN resultant, ≤ 20 Nm torsion); (2) applicability is limited to the composite femur analog and stem sizes 5–7; (3) the model must not be used for per-patient risk assessment, fatigue life prediction, or extreme-activity analysis without additional evidence per the maturation roadmap in Appendix A4.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
